--- a/AI_QRS_Defect_Tracker.xlsx
+++ b/AI_QRS_Defect_Tracker.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -83,8 +83,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +109,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6A000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -178,6 +192,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col width="8" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -1065,6 +1082,248 @@
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>--- Milestone 3 Defects ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Root Cause</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Date Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>DEF-M3-01</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>M3.2</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>retrieval_agent.py</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>0 chunks retrieved on all queries</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>similarity_threshold default=0.0 ignored settings value, passed as None to retriever which then used 0.3 but pronoun queries yielded near-zero similarity</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Changed default from 0.0 to None; added resolved_query param</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>DEF-M3-02</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>M3.2</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>conversation_memory_agent.py</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Pronoun it resolved to ACME (company name) instead of topic</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>resolve_references() used last_entities[0] = first capitalised word from LLM response (e.g. ACME CORPORATION POLICY)</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Rewrote priority: active_key_terms first, filtered boilerplate from entities</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>DEF-M3-03</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>M3.2</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>orchestrator.py</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>UnboundLocalError: resolved_query referenced before assignment in clarification cycle</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>resolved_query only assigned in else branch which was a comment, not code</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Always assign: refined_query if clarification cycle, else memory_resolved_query</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>DEF-M3-04</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>M3.2</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>orchestrator.py</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Memory-resolved query not passed to retrieval agent</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>resolved_query existed but was not forwarded to retrieval_agent.retrieve()</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Added resolved_query parameter to retrieval agent call</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
